--- a/artfynd/A 19680-2026 artfynd.xlsx
+++ b/artfynd/A 19680-2026 artfynd.xlsx
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133883501</v>
+        <v>133883527</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>80479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527232</v>
+        <v>527381</v>
       </c>
       <c r="R5" t="n">
-        <v>6956472</v>
+        <v>6956299</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883527</v>
+        <v>133883522</v>
       </c>
       <c r="B6" t="n">
-        <v>80479</v>
+        <v>91960</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527381</v>
+        <v>527456</v>
       </c>
       <c r="R6" t="n">
-        <v>6956299</v>
+        <v>6956461</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,32 +1195,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133883522</v>
+        <v>133883532</v>
       </c>
       <c r="B7" t="n">
-        <v>91960</v>
+        <v>75326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527456</v>
+        <v>527418</v>
       </c>
       <c r="R7" t="n">
-        <v>6956461</v>
+        <v>6956348</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,32 +1297,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133883532</v>
+        <v>133883515</v>
       </c>
       <c r="B8" t="n">
-        <v>75326</v>
+        <v>89340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6428</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527418</v>
+        <v>527353</v>
       </c>
       <c r="R8" t="n">
-        <v>6956348</v>
+        <v>6956305</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1593,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133883499</v>
+        <v>133883273</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>80474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,21 +1599,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1628,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527523</v>
+        <v>527349</v>
       </c>
       <c r="R11" t="n">
-        <v>6956607</v>
+        <v>6956460</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1663,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Riklig förekomst, med apothecier, på sälg och grenar av gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133883515</v>
+        <v>133883266</v>
       </c>
       <c r="B12" t="n">
-        <v>89340</v>
+        <v>83208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1701,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527353</v>
+        <v>527415</v>
       </c>
       <c r="R12" t="n">
-        <v>6956305</v>
+        <v>6956537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1774,6 +1769,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1792,32 +1788,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133883266</v>
+        <v>133883523</v>
       </c>
       <c r="B13" t="n">
-        <v>83208</v>
+        <v>92185</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1827,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527415</v>
+        <v>527354</v>
       </c>
       <c r="R13" t="n">
-        <v>6956537</v>
+        <v>6956273</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,7 +1867,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1890,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133883505</v>
+        <v>133883283</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>83344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1901,34 +1896,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bröcklingberget, Jmt</t>
+          <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527205</v>
+        <v>527416</v>
       </c>
       <c r="R14" t="n">
-        <v>6956487</v>
+        <v>6956424</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1963,17 +1958,13 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1992,32 +1983,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883273</v>
+        <v>133883529</v>
       </c>
       <c r="B15" t="n">
-        <v>80474</v>
+        <v>80479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,10 +2018,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527349</v>
+        <v>527495</v>
       </c>
       <c r="R15" t="n">
-        <v>6956460</v>
+        <v>6956514</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,11 +2054,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, med apothecier, på sälg och grenar av gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2094,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133883509</v>
+        <v>133883292</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>80474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2105,21 +2091,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2129,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527485</v>
+        <v>527462</v>
       </c>
       <c r="R16" t="n">
-        <v>6956429</v>
+        <v>6956590</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,11 +2151,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2196,10 +2177,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133883512</v>
+        <v>133883289</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2207,21 +2188,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2231,10 +2212,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527516</v>
+        <v>527444</v>
       </c>
       <c r="R17" t="n">
-        <v>6956490</v>
+        <v>6956497</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2267,11 +2248,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,10 +2274,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133883524</v>
+        <v>133883264</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>78368</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2309,21 +2285,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2333,10 +2309,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527435</v>
+        <v>527525</v>
       </c>
       <c r="R18" t="n">
-        <v>6956315</v>
+        <v>6956578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2369,11 +2345,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2400,10 +2371,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133883523</v>
+        <v>133883265</v>
       </c>
       <c r="B19" t="n">
-        <v>92185</v>
+        <v>80479</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2411,21 +2382,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2435,10 +2406,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527354</v>
+        <v>527464</v>
       </c>
       <c r="R19" t="n">
-        <v>6956273</v>
+        <v>6956533</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2471,6 +2442,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2497,10 +2473,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133883283</v>
+        <v>133883291</v>
       </c>
       <c r="B20" t="n">
-        <v>83344</v>
+        <v>57972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2508,34 +2484,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kojviken, Jmt</t>
+          <t>Bröcklingberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527416</v>
+        <v>527479</v>
       </c>
       <c r="R20" t="n">
-        <v>6956424</v>
+        <v>6956530</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,7 +2552,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2595,32 +2570,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133883529</v>
+        <v>133883544</v>
       </c>
       <c r="B21" t="n">
-        <v>80479</v>
+        <v>89340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2630,10 +2605,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527495</v>
+        <v>527408</v>
       </c>
       <c r="R21" t="n">
-        <v>6956514</v>
+        <v>6956382</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2692,32 +2667,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133883504</v>
+        <v>133883530</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>75326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2727,10 +2702,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527205</v>
+        <v>527482</v>
       </c>
       <c r="R22" t="n">
-        <v>6956496</v>
+        <v>6956546</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,11 +2738,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2794,10 +2764,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133883513</v>
+        <v>133883267</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2805,21 +2775,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2829,10 +2799,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527555</v>
+        <v>527428</v>
       </c>
       <c r="R23" t="n">
-        <v>6956570</v>
+        <v>6956495</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2865,11 +2835,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2896,10 +2861,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133883506</v>
+        <v>133883519</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2907,21 +2872,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2931,10 +2896,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527205</v>
+        <v>527405</v>
       </c>
       <c r="R24" t="n">
-        <v>6956484</v>
+        <v>6956470</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2967,11 +2932,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2998,10 +2958,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133883264</v>
+        <v>133883535</v>
       </c>
       <c r="B25" t="n">
-        <v>78368</v>
+        <v>79359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3009,21 +2969,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3033,10 +2993,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527525</v>
+        <v>527451</v>
       </c>
       <c r="R25" t="n">
-        <v>6956578</v>
+        <v>6956428</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3069,6 +3029,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;1000 bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3095,10 +3060,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133883289</v>
+        <v>133883534</v>
       </c>
       <c r="B26" t="n">
-        <v>91960</v>
+        <v>79359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3106,21 +3071,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3130,10 +3095,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527444</v>
+        <v>527463</v>
       </c>
       <c r="R26" t="n">
-        <v>6956497</v>
+        <v>6956485</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3166,6 +3131,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3192,32 +3162,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133883291</v>
+        <v>133883274</v>
       </c>
       <c r="B27" t="n">
-        <v>57972</v>
+        <v>91923</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3227,10 +3197,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527479</v>
+        <v>527426</v>
       </c>
       <c r="R27" t="n">
-        <v>6956530</v>
+        <v>6956484</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3289,32 +3259,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133883265</v>
+        <v>133883286</v>
       </c>
       <c r="B28" t="n">
-        <v>80479</v>
+        <v>79359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3324,10 +3294,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527464</v>
+        <v>527334</v>
       </c>
       <c r="R28" t="n">
-        <v>6956533</v>
+        <v>6956320</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3360,11 +3330,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3391,32 +3356,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133883292</v>
+        <v>133883270</v>
       </c>
       <c r="B29" t="n">
-        <v>80474</v>
+        <v>91923</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3426,10 +3391,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527462</v>
+        <v>527408</v>
       </c>
       <c r="R29" t="n">
-        <v>6956590</v>
+        <v>6956451</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,32 +3453,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133883267</v>
+        <v>133883545</v>
       </c>
       <c r="B30" t="n">
-        <v>79359</v>
+        <v>79615</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3523,10 +3488,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527428</v>
+        <v>527430</v>
       </c>
       <c r="R30" t="n">
-        <v>6956495</v>
+        <v>6956358</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3585,32 +3550,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133883530</v>
+        <v>133883514</v>
       </c>
       <c r="B31" t="n">
-        <v>75326</v>
+        <v>89340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6428</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3620,10 +3585,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527482</v>
+        <v>527445</v>
       </c>
       <c r="R31" t="n">
-        <v>6956546</v>
+        <v>6956549</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3682,32 +3647,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133883544</v>
+        <v>133883531</v>
       </c>
       <c r="B32" t="n">
-        <v>89340</v>
+        <v>75326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>6428</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3717,10 +3682,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527408</v>
+        <v>527313</v>
       </c>
       <c r="R32" t="n">
-        <v>6956382</v>
+        <v>6956377</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3779,10 +3744,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133883519</v>
+        <v>133883533</v>
       </c>
       <c r="B33" t="n">
-        <v>91960</v>
+        <v>80474</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3790,21 +3755,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3814,10 +3779,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527405</v>
+        <v>527421</v>
       </c>
       <c r="R33" t="n">
-        <v>6956470</v>
+        <v>6956360</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3876,7 +3841,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133883535</v>
+        <v>133883287</v>
       </c>
       <c r="B34" t="n">
         <v>79359</v>
@@ -3911,10 +3876,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527451</v>
+        <v>527292</v>
       </c>
       <c r="R34" t="n">
-        <v>6956428</v>
+        <v>6956372</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3947,11 +3912,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;1000 bålar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3978,32 +3938,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133883534</v>
+        <v>133883518</v>
       </c>
       <c r="B35" t="n">
-        <v>79359</v>
+        <v>91923</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4013,10 +3973,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527463</v>
+        <v>527404</v>
       </c>
       <c r="R35" t="n">
-        <v>6956485</v>
+        <v>6956471</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4049,11 +4009,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4080,10 +4035,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133883270</v>
+        <v>133883528</v>
       </c>
       <c r="B36" t="n">
-        <v>91923</v>
+        <v>80479</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4091,21 +4046,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4115,10 +4070,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527408</v>
+        <v>527413</v>
       </c>
       <c r="R36" t="n">
-        <v>6956451</v>
+        <v>6956400</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4177,32 +4132,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133883274</v>
+        <v>133883521</v>
       </c>
       <c r="B37" t="n">
-        <v>91923</v>
+        <v>91960</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4212,10 +4167,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527426</v>
+        <v>527367</v>
       </c>
       <c r="R37" t="n">
-        <v>6956484</v>
+        <v>6956568</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4274,32 +4229,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133883500</v>
+        <v>133883269</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>91923</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4309,10 +4264,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527225</v>
+        <v>527424</v>
       </c>
       <c r="R38" t="n">
-        <v>6956504</v>
+        <v>6956445</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4345,11 +4300,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4376,10 +4326,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133883510</v>
+        <v>133883271</v>
       </c>
       <c r="B39" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4387,16 +4337,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4411,10 +4361,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527512</v>
+        <v>527329</v>
       </c>
       <c r="R39" t="n">
-        <v>6956471</v>
+        <v>6956440</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4447,11 +4397,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4478,32 +4423,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133883286</v>
+        <v>133883290</v>
       </c>
       <c r="B40" t="n">
-        <v>79359</v>
+        <v>92185</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4513,10 +4458,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527334</v>
+        <v>527426</v>
       </c>
       <c r="R40" t="n">
-        <v>6956320</v>
+        <v>6956518</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4575,32 +4520,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133883545</v>
+        <v>133883268</v>
       </c>
       <c r="B41" t="n">
-        <v>79615</v>
+        <v>79359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4610,10 +4555,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527430</v>
+        <v>527423</v>
       </c>
       <c r="R41" t="n">
-        <v>6956358</v>
+        <v>6956494</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4646,6 +4591,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>80 cm lång</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4672,32 +4622,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133883531</v>
+        <v>133883501</v>
       </c>
       <c r="B42" t="n">
-        <v>75326</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4707,10 +4657,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527313</v>
+        <v>527232</v>
       </c>
       <c r="R42" t="n">
-        <v>6956377</v>
+        <v>6956472</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4743,6 +4693,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4769,10 +4724,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133883514</v>
+        <v>133883499</v>
       </c>
       <c r="B43" t="n">
-        <v>89340</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4780,21 +4735,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4804,10 +4759,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527445</v>
+        <v>527523</v>
       </c>
       <c r="R43" t="n">
-        <v>6956549</v>
+        <v>6956607</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4840,6 +4795,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4866,10 +4826,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133883533</v>
+        <v>133883505</v>
       </c>
       <c r="B44" t="n">
-        <v>80474</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4877,21 +4837,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4901,10 +4861,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527421</v>
+        <v>527205</v>
       </c>
       <c r="R44" t="n">
-        <v>6956360</v>
+        <v>6956487</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4937,6 +4897,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4963,7 +4928,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133883502</v>
+        <v>133883512</v>
       </c>
       <c r="B45" t="n">
         <v>57975</v>
@@ -4998,10 +4963,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527233</v>
+        <v>527516</v>
       </c>
       <c r="R45" t="n">
-        <v>6956477</v>
+        <v>6956490</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5065,7 +5030,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133883525</v>
+        <v>133883509</v>
       </c>
       <c r="B46" t="n">
         <v>57975</v>
@@ -5100,10 +5065,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527429</v>
+        <v>527485</v>
       </c>
       <c r="R46" t="n">
-        <v>6956308</v>
+        <v>6956429</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5140,7 +5105,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5167,10 +5132,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133883287</v>
+        <v>133883524</v>
       </c>
       <c r="B47" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5178,21 +5143,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5202,10 +5167,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527292</v>
+        <v>527435</v>
       </c>
       <c r="R47" t="n">
-        <v>6956372</v>
+        <v>6956315</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5238,6 +5203,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5264,32 +5234,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133883518</v>
+        <v>133883513</v>
       </c>
       <c r="B48" t="n">
-        <v>91923</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5299,10 +5269,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527404</v>
+        <v>527555</v>
       </c>
       <c r="R48" t="n">
-        <v>6956471</v>
+        <v>6956570</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5335,6 +5305,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5361,32 +5336,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133883528</v>
+        <v>133883504</v>
       </c>
       <c r="B49" t="n">
-        <v>80479</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5396,10 +5371,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527413</v>
+        <v>527205</v>
       </c>
       <c r="R49" t="n">
-        <v>6956400</v>
+        <v>6956496</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5432,6 +5407,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5458,10 +5438,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133883521</v>
+        <v>133883506</v>
       </c>
       <c r="B50" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5469,21 +5449,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5493,10 +5473,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527367</v>
+        <v>527205</v>
       </c>
       <c r="R50" t="n">
-        <v>6956568</v>
+        <v>6956484</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5529,6 +5509,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5555,32 +5540,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133883269</v>
+        <v>133883510</v>
       </c>
       <c r="B51" t="n">
-        <v>91923</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5590,10 +5575,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527424</v>
+        <v>527512</v>
       </c>
       <c r="R51" t="n">
-        <v>6956445</v>
+        <v>6956471</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5626,6 +5611,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5652,7 +5642,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133883507</v>
+        <v>133883500</v>
       </c>
       <c r="B52" t="n">
         <v>57975</v>
@@ -5687,10 +5677,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527426</v>
+        <v>527225</v>
       </c>
       <c r="R52" t="n">
-        <v>6956300</v>
+        <v>6956504</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5727,7 +5717,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5754,10 +5744,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133883271</v>
+        <v>133883525</v>
       </c>
       <c r="B53" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5765,16 +5755,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5789,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527329</v>
+        <v>527429</v>
       </c>
       <c r="R53" t="n">
-        <v>6956440</v>
+        <v>6956308</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5825,6 +5815,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5851,7 +5846,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133883508</v>
+        <v>133883502</v>
       </c>
       <c r="B54" t="n">
         <v>57975</v>
@@ -5886,10 +5881,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527433</v>
+        <v>527233</v>
       </c>
       <c r="R54" t="n">
-        <v>6956315</v>
+        <v>6956477</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5953,32 +5948,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133883290</v>
+        <v>133883507</v>
       </c>
       <c r="B55" t="n">
-        <v>92185</v>
+        <v>57975</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5991,7 +5986,7 @@
         <v>527426</v>
       </c>
       <c r="R55" t="n">
-        <v>6956518</v>
+        <v>6956300</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6024,6 +6019,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6050,10 +6050,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133883268</v>
+        <v>133883508</v>
       </c>
       <c r="B56" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6061,21 +6061,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527423</v>
+        <v>527433</v>
       </c>
       <c r="R56" t="n">
-        <v>6956494</v>
+        <v>6956315</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>80 cm lång</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 19680-2026 artfynd.xlsx
+++ b/artfynd/A 19680-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>133883293</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133883527</v>
+        <v>133883522</v>
       </c>
       <c r="B5" t="n">
-        <v>80479</v>
+        <v>91967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527381</v>
+        <v>527456</v>
       </c>
       <c r="R5" t="n">
-        <v>6956299</v>
+        <v>6956461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883522</v>
+        <v>133883527</v>
       </c>
       <c r="B6" t="n">
-        <v>91960</v>
+        <v>80486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527456</v>
+        <v>527381</v>
       </c>
       <c r="R6" t="n">
-        <v>6956461</v>
+        <v>6956299</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,32 +1195,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133883532</v>
+        <v>133883515</v>
       </c>
       <c r="B7" t="n">
-        <v>75326</v>
+        <v>89347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6428</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527418</v>
+        <v>527353</v>
       </c>
       <c r="R7" t="n">
-        <v>6956348</v>
+        <v>6956305</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,32 +1292,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133883515</v>
+        <v>133883532</v>
       </c>
       <c r="B8" t="n">
-        <v>89340</v>
+        <v>75333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>6428</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527353</v>
+        <v>527418</v>
       </c>
       <c r="R8" t="n">
-        <v>6956305</v>
+        <v>6956348</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,7 +1397,7 @@
         <v>133883516</v>
       </c>
       <c r="B9" t="n">
-        <v>89340</v>
+        <v>89347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>133883288</v>
       </c>
       <c r="B10" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133883273</v>
+        <v>133883266</v>
       </c>
       <c r="B11" t="n">
-        <v>80474</v>
+        <v>83215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,21 +1599,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527349</v>
+        <v>527415</v>
       </c>
       <c r="R11" t="n">
-        <v>6956460</v>
+        <v>6956537</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,17 +1661,13 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, med apothecier, på sälg och grenar av gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1690,10 +1686,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133883266</v>
+        <v>133883273</v>
       </c>
       <c r="B12" t="n">
-        <v>83208</v>
+        <v>80481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,21 +1697,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1725,10 +1721,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527415</v>
+        <v>527349</v>
       </c>
       <c r="R12" t="n">
-        <v>6956537</v>
+        <v>6956460</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,13 +1759,17 @@
           <t>2026-05-15</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, med apothecier, på sälg och grenar av gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>133883523</v>
       </c>
       <c r="B13" t="n">
-        <v>92185</v>
+        <v>92192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>133883283</v>
       </c>
       <c r="B14" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>133883529</v>
       </c>
       <c r="B15" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133883292</v>
+        <v>133883289</v>
       </c>
       <c r="B16" t="n">
-        <v>80474</v>
+        <v>91967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527462</v>
+        <v>527444</v>
       </c>
       <c r="R16" t="n">
-        <v>6956590</v>
+        <v>6956497</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2177,32 +2177,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133883289</v>
+        <v>133883265</v>
       </c>
       <c r="B17" t="n">
-        <v>91960</v>
+        <v>80486</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527444</v>
+        <v>527464</v>
       </c>
       <c r="R17" t="n">
-        <v>6956497</v>
+        <v>6956533</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2248,6 +2248,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2274,10 +2279,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133883264</v>
+        <v>133883292</v>
       </c>
       <c r="B18" t="n">
-        <v>78368</v>
+        <v>80481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2285,21 +2290,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2309,10 +2314,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527525</v>
+        <v>527462</v>
       </c>
       <c r="R18" t="n">
-        <v>6956578</v>
+        <v>6956590</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2371,32 +2376,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133883265</v>
+        <v>133883264</v>
       </c>
       <c r="B19" t="n">
-        <v>80479</v>
+        <v>78375</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2406,10 +2411,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527464</v>
+        <v>527525</v>
       </c>
       <c r="R19" t="n">
-        <v>6956533</v>
+        <v>6956578</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2442,11 +2447,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2570,10 +2570,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133883544</v>
+        <v>133883267</v>
       </c>
       <c r="B21" t="n">
-        <v>89340</v>
+        <v>79366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2581,21 +2581,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527408</v>
+        <v>527428</v>
       </c>
       <c r="R21" t="n">
-        <v>6956382</v>
+        <v>6956495</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2667,32 +2667,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133883530</v>
+        <v>133883544</v>
       </c>
       <c r="B22" t="n">
-        <v>75326</v>
+        <v>89347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6428</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527482</v>
+        <v>527408</v>
       </c>
       <c r="R22" t="n">
-        <v>6956546</v>
+        <v>6956382</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2764,32 +2764,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133883267</v>
+        <v>133883530</v>
       </c>
       <c r="B23" t="n">
-        <v>79359</v>
+        <v>75333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527428</v>
+        <v>527482</v>
       </c>
       <c r="R23" t="n">
-        <v>6956495</v>
+        <v>6956546</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133883519</v>
+        <v>133883535</v>
       </c>
       <c r="B24" t="n">
-        <v>91960</v>
+        <v>79366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527405</v>
+        <v>527451</v>
       </c>
       <c r="R24" t="n">
-        <v>6956470</v>
+        <v>6956428</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2932,6 +2932,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;1000 bålar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2958,10 +2963,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133883535</v>
+        <v>133883519</v>
       </c>
       <c r="B25" t="n">
-        <v>79359</v>
+        <v>91967</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2969,21 +2974,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2993,10 +2998,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527451</v>
+        <v>527405</v>
       </c>
       <c r="R25" t="n">
-        <v>6956428</v>
+        <v>6956470</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3029,11 +3034,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;1000 bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3063,7 +3063,7 @@
         <v>133883534</v>
       </c>
       <c r="B26" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3162,32 +3162,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133883274</v>
+        <v>133883286</v>
       </c>
       <c r="B27" t="n">
-        <v>91923</v>
+        <v>79366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527426</v>
+        <v>527334</v>
       </c>
       <c r="R27" t="n">
-        <v>6956484</v>
+        <v>6956320</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3259,32 +3259,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133883286</v>
+        <v>133883274</v>
       </c>
       <c r="B28" t="n">
-        <v>79359</v>
+        <v>91930</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527334</v>
+        <v>527426</v>
       </c>
       <c r="R28" t="n">
-        <v>6956320</v>
+        <v>6956484</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3359,7 +3359,7 @@
         <v>133883270</v>
       </c>
       <c r="B29" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133883545</v>
+        <v>133883531</v>
       </c>
       <c r="B30" t="n">
-        <v>79615</v>
+        <v>75333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3464,21 +3464,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6459</v>
+        <v>6428</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527430</v>
+        <v>527313</v>
       </c>
       <c r="R30" t="n">
-        <v>6956358</v>
+        <v>6956377</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3550,32 +3550,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133883514</v>
+        <v>133883545</v>
       </c>
       <c r="B31" t="n">
-        <v>89340</v>
+        <v>79622</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>6459</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527445</v>
+        <v>527430</v>
       </c>
       <c r="R31" t="n">
-        <v>6956549</v>
+        <v>6956358</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3647,32 +3647,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133883531</v>
+        <v>133883514</v>
       </c>
       <c r="B32" t="n">
-        <v>75326</v>
+        <v>89347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6428</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527313</v>
+        <v>527445</v>
       </c>
       <c r="R32" t="n">
-        <v>6956377</v>
+        <v>6956549</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3747,7 +3747,7 @@
         <v>133883533</v>
       </c>
       <c r="B33" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3841,32 +3841,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133883287</v>
+        <v>133883518</v>
       </c>
       <c r="B34" t="n">
-        <v>79359</v>
+        <v>91930</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527292</v>
+        <v>527404</v>
       </c>
       <c r="R34" t="n">
-        <v>6956372</v>
+        <v>6956471</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3938,32 +3938,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133883518</v>
+        <v>133883287</v>
       </c>
       <c r="B35" t="n">
-        <v>91923</v>
+        <v>79366</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527404</v>
+        <v>527292</v>
       </c>
       <c r="R35" t="n">
-        <v>6956471</v>
+        <v>6956372</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4038,7 +4038,7 @@
         <v>133883528</v>
       </c>
       <c r="B36" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>133883521</v>
       </c>
       <c r="B37" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>133883269</v>
       </c>
       <c r="B38" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4423,32 +4423,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133883290</v>
+        <v>133883268</v>
       </c>
       <c r="B40" t="n">
-        <v>92185</v>
+        <v>79366</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527426</v>
+        <v>527423</v>
       </c>
       <c r="R40" t="n">
-        <v>6956518</v>
+        <v>6956494</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4494,6 +4494,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>80 cm lång</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4520,32 +4525,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133883268</v>
+        <v>133883290</v>
       </c>
       <c r="B41" t="n">
-        <v>79359</v>
+        <v>92192</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4555,10 +4560,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527423</v>
+        <v>527426</v>
       </c>
       <c r="R41" t="n">
-        <v>6956494</v>
+        <v>6956518</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4591,11 +4596,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>80 cm lång</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5234,7 +5234,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133883513</v>
+        <v>133883504</v>
       </c>
       <c r="B48" t="n">
         <v>57975</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527555</v>
+        <v>527205</v>
       </c>
       <c r="R48" t="n">
-        <v>6956570</v>
+        <v>6956496</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5336,7 +5336,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133883504</v>
+        <v>133883513</v>
       </c>
       <c r="B49" t="n">
         <v>57975</v>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527205</v>
+        <v>527555</v>
       </c>
       <c r="R49" t="n">
-        <v>6956496</v>
+        <v>6956570</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5744,7 +5744,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133883525</v>
+        <v>133883502</v>
       </c>
       <c r="B53" t="n">
         <v>57975</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527429</v>
+        <v>527233</v>
       </c>
       <c r="R53" t="n">
-        <v>6956308</v>
+        <v>6956477</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5846,7 +5846,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133883502</v>
+        <v>133883525</v>
       </c>
       <c r="B54" t="n">
         <v>57975</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527233</v>
+        <v>527429</v>
       </c>
       <c r="R54" t="n">
-        <v>6956477</v>
+        <v>6956308</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 19680-2026 artfynd.xlsx
+++ b/artfynd/A 19680-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68488314</v>
+        <v>133883514</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bräcke, Jmt</t>
+          <t>Bröcklingberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527537.5488096364</v>
+        <v>527445</v>
       </c>
       <c r="R2" t="n">
-        <v>6956600.584593333</v>
+        <v>6956549</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-10-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-10-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttl till rikl</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,62 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68488361</v>
+        <v>133883515</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräcke, Jmt</t>
+          <t>Bröcklingberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527561.118588699</v>
+        <v>527353</v>
       </c>
       <c r="R3" t="n">
-        <v>6956581.985115401</v>
+        <v>6956305</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-10-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-10-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133883293</v>
+        <v>133883516</v>
       </c>
       <c r="B4" t="n">
-        <v>79366</v>
+        <v>89354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527522</v>
+        <v>527502</v>
       </c>
       <c r="R4" t="n">
-        <v>6956559</v>
+        <v>6956471</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133883522</v>
+        <v>133883544</v>
       </c>
       <c r="B5" t="n">
-        <v>91967</v>
+        <v>89354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527456</v>
+        <v>527408</v>
       </c>
       <c r="R5" t="n">
-        <v>6956461</v>
+        <v>6956382</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883527</v>
+        <v>133883289</v>
       </c>
       <c r="B6" t="n">
-        <v>80486</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527381</v>
+        <v>527444</v>
       </c>
       <c r="R6" t="n">
-        <v>6956299</v>
+        <v>6956497</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133883515</v>
+        <v>133883519</v>
       </c>
       <c r="B7" t="n">
-        <v>89347</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527353</v>
+        <v>527405</v>
       </c>
       <c r="R7" t="n">
-        <v>6956305</v>
+        <v>6956470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133883532</v>
+        <v>133883521</v>
       </c>
       <c r="B8" t="n">
-        <v>75333</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527418</v>
+        <v>527367</v>
       </c>
       <c r="R8" t="n">
-        <v>6956348</v>
+        <v>6956568</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,11 +1328,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133883516</v>
+        <v>133883522</v>
       </c>
       <c r="B9" t="n">
-        <v>89347</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527502</v>
+        <v>527456</v>
       </c>
       <c r="R9" t="n">
-        <v>6956471</v>
+        <v>6956461</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133883288</v>
+        <v>133883266</v>
       </c>
       <c r="B10" t="n">
-        <v>83351</v>
+        <v>83222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1529,7 +1489,7 @@
         <v>527415</v>
       </c>
       <c r="R10" t="n">
-        <v>6956488</v>
+        <v>6956537</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1570,6 +1530,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1588,32 +1549,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133883266</v>
+        <v>133883290</v>
       </c>
       <c r="B11" t="n">
-        <v>83215</v>
+        <v>92199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527415</v>
+        <v>527426</v>
       </c>
       <c r="R11" t="n">
-        <v>6956537</v>
+        <v>6956518</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1667,7 +1628,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1686,32 +1646,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133883273</v>
+        <v>133883523</v>
       </c>
       <c r="B12" t="n">
-        <v>80481</v>
+        <v>92199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1721,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527349</v>
+        <v>527354</v>
       </c>
       <c r="R12" t="n">
-        <v>6956460</v>
+        <v>6956273</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,11 +1717,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, med apothecier, på sälg och grenar av gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1788,10 +1743,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133883523</v>
+        <v>133883269</v>
       </c>
       <c r="B13" t="n">
-        <v>92192</v>
+        <v>91937</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1754,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527354</v>
+        <v>527424</v>
       </c>
       <c r="R13" t="n">
-        <v>6956273</v>
+        <v>6956445</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,45 +1840,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133883283</v>
+        <v>133883270</v>
       </c>
       <c r="B14" t="n">
-        <v>83351</v>
+        <v>91937</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kojviken, Jmt</t>
+          <t>Bröcklingberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527416</v>
+        <v>527408</v>
       </c>
       <c r="R14" t="n">
-        <v>6956424</v>
+        <v>6956451</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1919,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1983,10 +1937,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883529</v>
+        <v>133883274</v>
       </c>
       <c r="B15" t="n">
-        <v>80486</v>
+        <v>91937</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,21 +1948,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2018,10 +1972,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527495</v>
+        <v>527426</v>
       </c>
       <c r="R15" t="n">
-        <v>6956514</v>
+        <v>6956484</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,32 +2034,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133883289</v>
+        <v>133883518</v>
       </c>
       <c r="B16" t="n">
-        <v>91967</v>
+        <v>91937</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2115,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527444</v>
+        <v>527404</v>
       </c>
       <c r="R16" t="n">
-        <v>6956497</v>
+        <v>6956471</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2177,45 +2131,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133883265</v>
+        <v>68488314</v>
       </c>
       <c r="B17" t="n">
-        <v>80486</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bröcklingberget, Jmt</t>
+          <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527464</v>
+        <v>527538</v>
       </c>
       <c r="R17" t="n">
-        <v>6956533</v>
+        <v>6956601</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,17 +2196,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2017-10-11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2017-10-11</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Måttl till rikl</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2267,44 +2221,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133883292</v>
+        <v>133883267</v>
       </c>
       <c r="B18" t="n">
-        <v>80481</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2314,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527462</v>
+        <v>527428</v>
       </c>
       <c r="R18" t="n">
-        <v>6956590</v>
+        <v>6956495</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2376,32 +2330,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133883264</v>
+        <v>133883268</v>
       </c>
       <c r="B19" t="n">
-        <v>78375</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2411,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527525</v>
+        <v>527423</v>
       </c>
       <c r="R19" t="n">
-        <v>6956578</v>
+        <v>6956494</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2447,6 +2401,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>80 cm lång</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2473,32 +2432,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133883291</v>
+        <v>133883286</v>
       </c>
       <c r="B20" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2508,10 +2467,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527479</v>
+        <v>527334</v>
       </c>
       <c r="R20" t="n">
-        <v>6956530</v>
+        <v>6956320</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2570,14 +2529,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133883267</v>
+        <v>133883287</v>
       </c>
       <c r="B21" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2605,10 +2564,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527428</v>
+        <v>527292</v>
       </c>
       <c r="R21" t="n">
-        <v>6956495</v>
+        <v>6956372</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2667,32 +2626,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133883544</v>
+        <v>133883293</v>
       </c>
       <c r="B22" t="n">
-        <v>89347</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2702,10 +2661,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527408</v>
+        <v>527522</v>
       </c>
       <c r="R22" t="n">
-        <v>6956382</v>
+        <v>6956559</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2764,32 +2723,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133883530</v>
+        <v>133883534</v>
       </c>
       <c r="B23" t="n">
-        <v>75333</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2799,10 +2758,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527482</v>
+        <v>527463</v>
       </c>
       <c r="R23" t="n">
-        <v>6956546</v>
+        <v>6956485</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2835,6 +2794,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2864,11 +2828,11 @@
         <v>133883535</v>
       </c>
       <c r="B24" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2963,32 +2927,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133883519</v>
+        <v>133883530</v>
       </c>
       <c r="B25" t="n">
-        <v>91967</v>
+        <v>75340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2998,10 +2962,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527405</v>
+        <v>527482</v>
       </c>
       <c r="R25" t="n">
-        <v>6956470</v>
+        <v>6956546</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3060,32 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133883534</v>
+        <v>133883531</v>
       </c>
       <c r="B26" t="n">
-        <v>79366</v>
+        <v>75340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3095,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527463</v>
+        <v>527313</v>
       </c>
       <c r="R26" t="n">
-        <v>6956485</v>
+        <v>6956377</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3131,11 +3095,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3162,32 +3121,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133883286</v>
+        <v>133883532</v>
       </c>
       <c r="B27" t="n">
-        <v>79366</v>
+        <v>75340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3197,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527334</v>
+        <v>527418</v>
       </c>
       <c r="R27" t="n">
-        <v>6956320</v>
+        <v>6956348</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3233,6 +3192,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3259,45 +3223,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133883274</v>
+        <v>133883283</v>
       </c>
       <c r="B28" t="n">
-        <v>91930</v>
+        <v>83358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bröcklingberget, Jmt</t>
+          <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527426</v>
+        <v>527416</v>
       </c>
       <c r="R28" t="n">
-        <v>6956484</v>
+        <v>6956424</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3338,6 +3302,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3356,32 +3321,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133883270</v>
+        <v>133883288</v>
       </c>
       <c r="B29" t="n">
-        <v>91930</v>
+        <v>83358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3391,10 +3356,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527408</v>
+        <v>527415</v>
       </c>
       <c r="R29" t="n">
-        <v>6956451</v>
+        <v>6956488</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3453,32 +3418,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133883531</v>
+        <v>133883273</v>
       </c>
       <c r="B30" t="n">
-        <v>75333</v>
+        <v>80488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3488,10 +3453,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527313</v>
+        <v>527349</v>
       </c>
       <c r="R30" t="n">
-        <v>6956377</v>
+        <v>6956460</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3524,6 +3489,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, med apothecier, på sälg och grenar av gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3550,32 +3520,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133883545</v>
+        <v>133883292</v>
       </c>
       <c r="B31" t="n">
-        <v>79622</v>
+        <v>80488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3585,10 +3555,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527430</v>
+        <v>527462</v>
       </c>
       <c r="R31" t="n">
-        <v>6956358</v>
+        <v>6956590</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3647,10 +3617,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133883514</v>
+        <v>133883533</v>
       </c>
       <c r="B32" t="n">
-        <v>89347</v>
+        <v>80488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3658,21 +3628,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3682,10 +3652,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527445</v>
+        <v>527421</v>
       </c>
       <c r="R32" t="n">
-        <v>6956549</v>
+        <v>6956360</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3744,32 +3714,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133883533</v>
+        <v>133883545</v>
       </c>
       <c r="B33" t="n">
-        <v>80481</v>
+        <v>79629</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3779,10 +3749,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527421</v>
+        <v>527430</v>
       </c>
       <c r="R33" t="n">
-        <v>6956360</v>
+        <v>6956358</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3841,10 +3811,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133883518</v>
+        <v>133883265</v>
       </c>
       <c r="B34" t="n">
-        <v>91930</v>
+        <v>80493</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3852,21 +3822,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3876,10 +3846,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527404</v>
+        <v>527464</v>
       </c>
       <c r="R34" t="n">
-        <v>6956471</v>
+        <v>6956533</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3912,6 +3882,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3938,32 +3913,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133883287</v>
+        <v>133883527</v>
       </c>
       <c r="B35" t="n">
-        <v>79366</v>
+        <v>80493</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3973,10 +3948,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527292</v>
+        <v>527381</v>
       </c>
       <c r="R35" t="n">
-        <v>6956372</v>
+        <v>6956299</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4038,7 +4013,7 @@
         <v>133883528</v>
       </c>
       <c r="B36" t="n">
-        <v>80486</v>
+        <v>80493</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4132,32 +4107,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133883521</v>
+        <v>133883529</v>
       </c>
       <c r="B37" t="n">
-        <v>91967</v>
+        <v>80493</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4167,10 +4142,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527367</v>
+        <v>527495</v>
       </c>
       <c r="R37" t="n">
-        <v>6956568</v>
+        <v>6956514</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4229,10 +4204,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133883269</v>
+        <v>133883271</v>
       </c>
       <c r="B38" t="n">
-        <v>91930</v>
+        <v>57972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4240,21 +4215,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4264,10 +4239,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527424</v>
+        <v>527329</v>
       </c>
       <c r="R38" t="n">
-        <v>6956445</v>
+        <v>6956440</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4326,14 +4301,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133883271</v>
+        <v>133883291</v>
       </c>
       <c r="B39" t="n">
         <v>57972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4361,10 +4336,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527329</v>
+        <v>527479</v>
       </c>
       <c r="R39" t="n">
-        <v>6956440</v>
+        <v>6956530</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4423,10 +4398,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133883268</v>
+        <v>133883499</v>
       </c>
       <c r="B40" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4434,21 +4409,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4458,10 +4433,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527423</v>
+        <v>527523</v>
       </c>
       <c r="R40" t="n">
-        <v>6956494</v>
+        <v>6956607</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4498,7 +4473,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>80 cm lång</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4525,32 +4500,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133883290</v>
+        <v>133883500</v>
       </c>
       <c r="B41" t="n">
-        <v>92192</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4560,10 +4535,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527426</v>
+        <v>527225</v>
       </c>
       <c r="R41" t="n">
-        <v>6956518</v>
+        <v>6956504</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4596,6 +4571,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4724,7 +4704,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133883499</v>
+        <v>133883502</v>
       </c>
       <c r="B43" t="n">
         <v>57975</v>
@@ -4759,10 +4739,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527523</v>
+        <v>527233</v>
       </c>
       <c r="R43" t="n">
-        <v>6956607</v>
+        <v>6956477</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4826,7 +4806,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133883505</v>
+        <v>133883504</v>
       </c>
       <c r="B44" t="n">
         <v>57975</v>
@@ -4864,7 +4844,7 @@
         <v>527205</v>
       </c>
       <c r="R44" t="n">
-        <v>6956487</v>
+        <v>6956496</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4901,7 +4881,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4928,7 +4908,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133883512</v>
+        <v>133883505</v>
       </c>
       <c r="B45" t="n">
         <v>57975</v>
@@ -4963,10 +4943,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527516</v>
+        <v>527205</v>
       </c>
       <c r="R45" t="n">
-        <v>6956490</v>
+        <v>6956487</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5003,7 +4983,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5030,7 +5010,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133883509</v>
+        <v>133883506</v>
       </c>
       <c r="B46" t="n">
         <v>57975</v>
@@ -5065,10 +5045,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527485</v>
+        <v>527205</v>
       </c>
       <c r="R46" t="n">
-        <v>6956429</v>
+        <v>6956484</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5105,7 +5085,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och något äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5132,7 +5112,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133883524</v>
+        <v>133883507</v>
       </c>
       <c r="B47" t="n">
         <v>57975</v>
@@ -5167,10 +5147,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527435</v>
+        <v>527426</v>
       </c>
       <c r="R47" t="n">
-        <v>6956315</v>
+        <v>6956300</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5207,7 +5187,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5234,7 +5214,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133883504</v>
+        <v>133883508</v>
       </c>
       <c r="B48" t="n">
         <v>57975</v>
@@ -5269,10 +5249,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527205</v>
+        <v>527433</v>
       </c>
       <c r="R48" t="n">
-        <v>6956496</v>
+        <v>6956315</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5309,7 +5289,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5336,7 +5316,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133883513</v>
+        <v>133883509</v>
       </c>
       <c r="B49" t="n">
         <v>57975</v>
@@ -5371,10 +5351,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527555</v>
+        <v>527485</v>
       </c>
       <c r="R49" t="n">
-        <v>6956570</v>
+        <v>6956429</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5411,7 +5391,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5438,7 +5418,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133883506</v>
+        <v>133883510</v>
       </c>
       <c r="B50" t="n">
         <v>57975</v>
@@ -5473,10 +5453,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527205</v>
+        <v>527512</v>
       </c>
       <c r="R50" t="n">
-        <v>6956484</v>
+        <v>6956471</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5513,7 +5493,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack färska och något äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5540,7 +5520,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133883510</v>
+        <v>133883512</v>
       </c>
       <c r="B51" t="n">
         <v>57975</v>
@@ -5575,10 +5555,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527512</v>
+        <v>527516</v>
       </c>
       <c r="R51" t="n">
-        <v>6956471</v>
+        <v>6956490</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5642,7 +5622,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133883500</v>
+        <v>133883513</v>
       </c>
       <c r="B52" t="n">
         <v>57975</v>
@@ -5677,10 +5657,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527225</v>
+        <v>527555</v>
       </c>
       <c r="R52" t="n">
-        <v>6956504</v>
+        <v>6956570</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5717,7 +5697,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5744,7 +5724,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133883502</v>
+        <v>133883524</v>
       </c>
       <c r="B53" t="n">
         <v>57975</v>
@@ -5779,10 +5759,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527233</v>
+        <v>527435</v>
       </c>
       <c r="R53" t="n">
-        <v>6956477</v>
+        <v>6956315</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5819,7 +5799,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5948,27 +5928,27 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133883507</v>
+        <v>132182473</v>
       </c>
       <c r="B55" t="n">
-        <v>57975</v>
+        <v>57165</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5976,20 +5956,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bröcklingberget, Jmt</t>
+          <t>Rönnberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527426</v>
+        <v>527394</v>
       </c>
       <c r="R55" t="n">
-        <v>6956300</v>
+        <v>6956672</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6013,17 +6005,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6038,57 +6035,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Robin Mårtensson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Robin Mårtensson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133883508</v>
+        <v>68488361</v>
       </c>
       <c r="B56" t="n">
-        <v>57975</v>
+        <v>97983</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bröcklingberget, Jmt</t>
+          <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527433</v>
+        <v>527561</v>
       </c>
       <c r="R56" t="n">
-        <v>6956315</v>
+        <v>6956582</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6115,17 +6112,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2017-10-10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>2017-10-10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6140,15 +6132,112 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>133883264</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78382</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Bröcklingberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>527525</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6956578</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19680-2026 artfynd.xlsx
+++ b/artfynd/A 19680-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883514</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883515</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883516</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883544</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883289</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883519</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883521</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883522</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883266</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883290</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883523</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883269</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,6 +1999,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883270</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2031,6 +2101,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883274</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2128,6 +2203,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883518</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2230,6 +2310,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68488314</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2327,6 +2412,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883267</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2429,6 +2519,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883268</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2526,6 +2621,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883286</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2623,6 +2723,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883287</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2720,6 +2825,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883293</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2822,6 +2932,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883534</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2924,6 +3039,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883535</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3021,6 +3141,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883530</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3118,6 +3243,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883531</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3220,6 +3350,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883532</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3318,6 +3453,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883283</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3415,6 +3555,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883288</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3517,6 +3662,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883273</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3614,6 +3764,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883292</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3711,6 +3866,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883533</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3808,6 +3968,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883545</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3910,6 +4075,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883265</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4007,6 +4177,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883527</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4104,6 +4279,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883528</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4201,6 +4381,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883529</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4298,6 +4483,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883271</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4395,6 +4585,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883291</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4497,6 +4692,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883499</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4599,6 +4799,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883500</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4701,6 +4906,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883501</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4803,6 +5013,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883502</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4905,6 +5120,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883504</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5007,6 +5227,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883505</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5109,6 +5334,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883506</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5211,6 +5441,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883507</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5313,6 +5548,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883508</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5415,6 +5655,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883509</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5517,6 +5762,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883510</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5619,6 +5869,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883512</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5721,6 +5976,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883513</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5823,6 +6083,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883524</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5925,6 +6190,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883525</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6044,6 +6314,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132182473</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6141,6 +6416,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68488361</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6238,8 +6518,71 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883264</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>